--- a/output/pdf_financials_xlsx/ACR.H.xlsx
+++ b/output/pdf_financials_xlsx/ACR.H.xlsx
@@ -5649,40 +5649,40 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.010067</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.010067</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.010067</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.010067</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.471494</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.479674</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.479674</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.479674</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.634924</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.6741740000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.6741740000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.026174</v>
+        <v>0.666824</v>
       </c>
     </row>
     <row r="93">
@@ -9194,7 +9194,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -15562,7 +15566,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17026,7 +17034,11 @@
           <t>Reserves 10,067</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18961,7 +18973,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -19501,7 +19517,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ACR.H.xlsx
+++ b/output/pdf_financials_xlsx/ACR.H.xlsx
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000265</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.002442</v>
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>5.8e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.015162</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003383</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001085</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.436939</v>
+        <v>-0.437204</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.198989</v>
@@ -2069,19 +2069,19 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.036513</v>
+        <v>-0.036571</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.11643</v>
+        <v>-3.131592</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.954156</v>
+        <v>-0.957539</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.055745</v>
+        <v>-0.05683</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.033363</v>
+        <v>-0.033457</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.436276</v>
+        <v>-0.436541</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.198989</v>
@@ -2193,19 +2193,19 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.036513</v>
+        <v>-0.036571</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.11643</v>
+        <v>-3.131592</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.954156</v>
+        <v>-0.957539</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.055745</v>
+        <v>-0.05683</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.033363</v>
+        <v>-0.033457</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2471,46 +2471,46 @@
         <v>0.748678</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.805926</v>
+        <v>0.574998</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.325018</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.171972</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.011697</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.011697</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.05568</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.402951</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.097495</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.030495</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001673</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004691</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.05264</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.030575</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.025695</v>
       </c>
     </row>
     <row r="35">
@@ -2575,46 +2575,46 @@
         <v>0.925319</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.808926</v>
+        <v>0.577998</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.325018</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.171972</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.011697</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.011697</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.05568</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.402951</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.097495</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.030495</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001673</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004691</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.05264</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.030575</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.025695</v>
       </c>
     </row>
     <row r="37">
@@ -3199,28 +3199,28 @@
         <v>0.01625</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.009950000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.325018</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.180775</v>
+        <v>0.008803</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.016047</v>
+        <v>0.00435</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.016047</v>
+        <v>0.00435</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.056247</v>
+        <v>0.000567</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.428006</v>
+        <v>0.025055</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.116902</v>
+        <v>0.019407</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">
